--- a/benchmark/notebooks/acq_method_tables.xlsx
+++ b/benchmark/notebooks/acq_method_tables.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -470,6 +470,10 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,10 +499,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>golinski</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>otl_circuit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>piston</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rastrigin_6d</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -525,12 +549,32 @@
           <t>0.0911 ± 0.057</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.56e-06 ± 8.5e-08</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>0.00413 ± 0.015</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.53e-06 ± 9.7e-07</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.000307 ± 0.00029</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.0322 ± 0.12</t>
         </is>
@@ -555,10 +599,30 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>1.24e-07 ± 1e-08</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.00858 ± 0.021</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>4.33e-07 ± 5.5e-07</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>1.24e-06 ± 9.2e-07</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.0326 ± 0.12</t>
         </is>
@@ -581,12 +645,32 @@
           <t>0.649 ± 1.1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>0.0912 ± 0.1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.00142 ± 0.0028</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0011 ± 0.0007</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.172 ± 0.33</t>
         </is>
@@ -609,12 +693,32 @@
           <t>0.0516 ± 0.088</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>0.00441 ± 0.015</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3.07e-05 ± 6.1e-05</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.000715 ± 0.00033</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>0.0168 ± 0.087</t>
         </is>
@@ -641,12 +745,32 @@
           <t>0.0697 ± 0.057</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>31.6 ± 17</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>0.000736 ± 0.0011</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.0242 ± 0.022</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00168 ± 0.001</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>0.000135 ± 0.00025</t>
         </is>
@@ -671,10 +795,30 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>0.941 ± 1.9</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>0.0395 ± 0.072</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.00164 ± 0.0012</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>0.000571 ± 0.00054</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.0345 ± 0.12</t>
         </is>
@@ -697,12 +841,32 @@
           <t>0.179 ± 0.42</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>0.026 ± 0.048</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>1.74e-05 ± 2.3e-05</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.000718 ± 0.00046</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>0.06 ± 0.18</t>
         </is>
@@ -725,12 +889,32 @@
           <t>0.0736 ± 0.088</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>0.000795 ± 0.0019</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.0155 ± 0.011</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00177 ± 0.00093</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>0.00107 ± 0.0013</t>
         </is>
@@ -757,12 +941,32 @@
           <t>0.0532 ± 0.054</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16.3 ± 17</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>3.11e-07 ± 3.7e-06</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.0565 ± 0.02</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.00339 ± 0.0033</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>7.92e-06 ± 3.3e-05</t>
         </is>
@@ -787,10 +991,30 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>0.000119 ± 0.00015</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>0.00697 ± 0.019</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.0119 ± 0.013</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.00174 ± 4e-06</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>0.0369 ± 0.12</t>
         </is>
@@ -813,12 +1037,32 @@
           <t>0.419 ± 0.71</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>0.0292 ± 0.049</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>0.00033 ± 0.00041</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>0.00131 ± 0.00074</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>23.6 ± 0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>0.0326 ± 0.12</t>
         </is>
@@ -841,12 +1085,32 @@
           <t>0.0898 ± 0.092</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>0.000435 ± 0.00059</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.0218 ± 0.018</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.00267 ± 0.00088</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>9.81 ± 0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>0.000441 ± 0.00073</t>
         </is>
@@ -875,10 +1139,30 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>3.75 ± 2.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>0.00464 ± 0.016</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.0268 ± 0.029</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.00378 ± 0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>0.000791 ± 0.0013</t>
         </is>
@@ -901,12 +1185,32 @@
           <t>0.0966 ± 0.12</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>0.0271 ± 0.049</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>0.000173 ± 0.00028</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>0.00163 ± 0.00073</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>0.0462 ± 0.18</t>
         </is>
@@ -929,12 +1233,32 @@
           <t>0.0842 ± 0.088</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>0.00088 ± 0.0015</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0203 ± 0.017</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.00189 ± 0.00073</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>0.000906 ± 0.0011</t>
         </is>
@@ -961,12 +1285,32 @@
           <t>0.078 ± 0.085</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.307 ± 0.61</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>0.0137 ± 0.024</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.0147 ± 0.012</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.00448 ± 0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>0.000224 ± 0.00067</t>
         </is>
@@ -989,12 +1333,32 @@
           <t>0.19 ± 0.39</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>0.0467 ± 0.061</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>0.000322 ± 0.0004</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>0.00254 ± 0.00099</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>0.0341 ± 0.12</t>
         </is>
@@ -1019,10 +1383,30 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>1.49 ± 3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>0.0267 ± 0.029</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.0146 ± 0.013</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.00295 ± 0.0018</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>0.00284 ± 0.0053</t>
         </is>
@@ -1049,12 +1433,32 @@
           <t>0.00249 ± 0.0073</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>9.65 ± 6.6</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>0.00853 ± 0.021</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>6.33e-07 ± 4.8e-07</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>0.017 ± 0.087</t>
         </is>
@@ -1079,10 +1483,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>56.7 ± 47</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>0.1 ± 0.12</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.00142 ± 0.0028</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.00112 ± 0.00073</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>0.188 ± 0.33</t>
         </is>
@@ -1105,12 +1529,32 @@
           <t>0.0269 ± 0.081</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>20 ± 29</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>0.00463 ± 0.015</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.23e-05 ± 2.5e-05</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>0.000713 ± 0.00054</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>0.000752 ± 0.002</t>
         </is>
@@ -1135,15 +1579,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1169,10 +1617,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>golinski</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>otl_circuit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>piston</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rastrigin_6d</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -1199,12 +1667,32 @@
           <t>0.00124 ± 0.0059</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.5e-06 ± 8.5e-08</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>0.00413 ± 0.015</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3.87e-06 ± 3.2e-06</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2.16e-07 ± 1.5e-07</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>28.3 ± 6.1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.0322 ± 0.12</t>
         </is>
@@ -1229,10 +1717,30 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>1.26e-07 ± 1.3e-09</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.0105 ± 0.023</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4.64e-07 ± 3.8e-07</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4.62e-07 ± 5.1e-07</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25 ± 5.7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.0323 ± 0.12</t>
         </is>
@@ -1255,12 +1763,32 @@
           <t>0.529 ± 0.88</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>0.0769 ± 0.094</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.00142 ± 0.0028</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00104 ± 0.00071</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>18.2 ± 9.6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.2 ± 0.33</t>
         </is>
@@ -1283,12 +1811,32 @@
           <t>0.0941 ± 0.12</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>0.0183 ± 0.06</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00105 ± 0.00023</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>6.49 ± 4.2</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>0.0185 ± 0.098</t>
         </is>
@@ -1315,12 +1863,32 @@
           <t>0.00462 ± 0.023</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>43.8 ± 0</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>0.0009 ± 0.0012</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.055 ± 0.03</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00127 ± 0.00052</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20.7 ± 6.8</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>0.000114 ± 0.00017</t>
         </is>
@@ -1345,10 +1913,30 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>1.37 ± 2.6</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>0.0426 ± 0.081</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.00558 ± 0.0096</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2.93e-05 ± 3.7e-05</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>23.4 ± 3.2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.0488 ± 0.15</t>
         </is>
@@ -1371,12 +1959,32 @@
           <t>0.238 ± 0.59</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>0.0349 ± 0.062</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>6.94e-05 ± 7e-05</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.000532 ± 0.00038</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13.6 ± 3.8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>0.0684 ± 0.19</t>
         </is>
@@ -1399,12 +2007,32 @@
           <t>0.0548 ± 0.066</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>0.0025 ± 0.011</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.0158 ± 0.011</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00125 ± 0.0011</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>3.87 ± 2.8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>0.000646 ± 0.0023</t>
         </is>
@@ -1431,12 +2059,32 @@
           <t>0.00181 ± 0.0076</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>37.3 ± 13</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>-6.54e-07 ± 4.2e-07</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.0659 ± 0.03</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0025 ± 0.0021</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30.6 ± 9.4</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1.81e-06 ± 5.8e-06</t>
         </is>
@@ -1461,10 +2109,30 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>6.39e-05 ± 7.9e-05</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>0.0225 ± 0.048</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.0121 ± 0.014</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.00109 ± 0.0006</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>31.2 ± 2.5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>0.0324 ± 0.12</t>
         </is>
@@ -1487,12 +2155,32 @@
           <t>0.662 ± 0.95</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>0.029 ± 0.049</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>3.07e-05 ± 6.1e-05</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>0.001 ± 0.00074</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12.2 ± 8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>0.0457 ± 0.18</t>
         </is>
@@ -1515,12 +2203,32 @@
           <t>0.158 ± 0.39</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>0.000174 ± 0.00025</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.0163 ± 0.014</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.00205 ± 0.00054</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>3.89 ± 2.2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>0.000521 ± 0.00094</t>
         </is>
@@ -1547,12 +2255,32 @@
           <t>0.0211 ± 0.035</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7.82 ± 4.1</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>0.00868 ± 0.021</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.0117 ± 0.013</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.00336 ± 0.0018</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30.4 ± 4.9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>0.0163 ± 0.087</t>
         </is>
@@ -1575,12 +2303,32 @@
           <t>0.434 ± 0.74</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>0.0288 ± 0.049</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>3.07e-05 ± 6.1e-05</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>0.000822 ± 0.00057</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9.46 ± 2.4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>0.0486 ± 0.15</t>
         </is>
@@ -1603,12 +2351,32 @@
           <t>0.0421 ± 0.048</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>0.0095 ± 0.021</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0155 ± 0.013</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.0026 ± 0.00096</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>4.8 ± 1.6</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>0.000346 ± 0.00085</t>
         </is>
@@ -1635,12 +2403,32 @@
           <t>0.00541 ± 0.014</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.965 ± 1.4</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>0.0194 ± 0.028</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.0039 ± 0.0073</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>0.00173 ± 0.0013</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>24.3 ± 5.9</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>6.35e-05 ± 0.00015</t>
         </is>
@@ -1663,12 +2451,32 @@
           <t>0.666 ± 1.1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>0.0413 ± 0.048</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>0.000162 ± 0.00029</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.00209 ± 0.0007</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12.6 ± 3.4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>0.000237 ± 0.00041</t>
         </is>
@@ -1691,12 +2499,32 @@
           <t>0.135 ± 0.41</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>0.0406 ± 0.049</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.0287 ± 0.017</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.00238 ± 0.0008</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>3.95 ± 2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>0.000346 ± 0.00089</t>
         </is>
@@ -1725,10 +2553,30 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>2.44 ± 2.5</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
           <t>0.0085 ± 0.021</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2.74e-07 ± 1.7e-07</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>4.58e-07 ± 5.5e-07</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20.5 ± 4.5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>0.0162 ± 0.087</t>
         </is>
@@ -1753,10 +2601,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>17.5 ± 28</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>0.0768 ± 0.094</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.00142 ± 0.0028</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.00123 ± 0.00062</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20.4 ± 7.4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>0.168 ± 0.3</t>
         </is>
@@ -1781,10 +2649,30 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>10.6 ± 4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>0.0411 ± 0.1</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.000715 ± 0.00033</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>5.19 ± 2.6</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>0.000219 ± 0.00055</t>
         </is>
@@ -1809,15 +2697,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1843,10 +2735,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>golinski</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>otl_circuit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>piston</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rastrigin_6d</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -1875,10 +2787,30 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>576 ± 3.9e-08</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>0.00608 ± 0.0012</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.000194 ± 5.3e-11</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.000247 ± 7.7e-06</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -1901,12 +2833,32 @@
           <t>26.6 ± 22</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>576 ± 4.9e-09</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>0.00576 ± 0.0016</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.000194 ± 1.7e-11</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.000256 ± 8.5e-09</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -1929,12 +2881,32 @@
           <t>23.7 ± 27</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>0.00892 ± 0.0073</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.000651 ± 0.00091</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>0.000183 ± 5.8e-05</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.0122 ± 0.015</t>
         </is>
@@ -1957,12 +2929,32 @@
           <t>10.8 ± 19</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>0.00608 ± 0.0012</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>0.000194 ± 0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.000236 ± 6.2e-06</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>0.00647 ± 0.0045</t>
         </is>
@@ -1991,10 +2983,30 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>597 ± 19</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>0.0064 ± 2.3e-06</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.000753 ± 0.00028</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>0.000196 ± 5e-05</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>0.00564 ± 1.8e-06</t>
         </is>
@@ -2019,10 +3031,30 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>576 ± 4e-05</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>0.0066 ± 0.0048</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.000514 ± 0.00032</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.000256 ± 2.3e-10</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -2045,12 +3077,32 @@
           <t>12.9 ± 19</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>0.00556 ± 0.0034</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>0.000194 ± 0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.00021 ± 4.2e-05</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>0.00663 ± 0.0045</t>
         </is>
@@ -2073,12 +3125,32 @@
           <t>15.9 ± 21</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>0.0064 ± 3.9e-06</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.000908 ± 0.0008</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.000202 ± 6.4e-05</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>0.00564 ± 5.3e-06</t>
         </is>
@@ -2107,10 +3179,30 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>584 ± 11</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>0.0064 ± 7.5e-09</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.00079 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.000175 ± 3.7e-05</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>0.00564 ± 4.8e-07</t>
         </is>
@@ -2135,10 +3227,30 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>576 ± 4e-06</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>0.00592 ± 0.0014</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.000514 ± 0.00032</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.000245 ± 1.1e-05</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -2161,12 +3273,32 @@
           <t>14.2 ± 18</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>0.00524 ± 0.0035</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>0.000275 ± 9.9e-05</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.000209 ± 5.3e-05</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4.72 ± 0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -2189,12 +3321,32 @@
           <t>17.3 ± 21</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>0.0064 ± 1.2e-06</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.000514 ± 0.00032</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>0.000173 ± 6.4e-05</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>1.15 ± 0</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 3.5e-06</t>
         </is>
@@ -2223,10 +3375,30 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>576 ± 9.1e-06</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>0.00608 ± 0.0012</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.000512 ± 0.00032</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>6.4e-05 ± 0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 4.8e-06</t>
         </is>
@@ -2249,12 +3421,32 @@
           <t>16.4 ± 21</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>0.0054 ± 0.0034</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>0.000235 ± 8.1e-05</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.000211 ± 3.7e-05</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>0.00662 ± 0.0045</t>
         </is>
@@ -2277,12 +3469,32 @@
           <t>14.9 ± 21</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>0.0064 ± 3.1e-06</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.000275 ± 0.0001</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.000185 ± 6.9e-05</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>0.00564 ± 5.1e-06</t>
         </is>
@@ -2311,10 +3523,30 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>576 ± 0.00033</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>0.00544 ± 0.0019</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.000275 ± 9.9e-05</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>5.89e-05 ± 0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 2.3e-06</t>
         </is>
@@ -2337,12 +3569,32 @@
           <t>13.6 ± 21</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>0.00505 ± 0.0045</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>0.000275 ± 9.9e-05</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.000161 ± 7.4e-05</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -2367,10 +3619,30 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
           <t>0.00465 ± 0.0023</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.000333 ± 0.00028</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.000153 ± 5.9e-05</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>0.00564 ± 7.5e-06</t>
         </is>
@@ -2399,10 +3671,30 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>576 ± 2.9e-06</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
           <t>0.00576 ± 0.0016</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.000194 ± 2.8e-11</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>0.00647 ± 0.0045</t>
         </is>
@@ -2427,10 +3719,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>592 ± 26</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>0.00839 ± 0.0071</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.000651 ± 0.00091</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>0.000198 ± 5.8e-05</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>0.0131 ± 0.016</t>
         </is>
@@ -2455,10 +3767,30 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>587 ± 22</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>0.00608 ± 0.0012</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>0.000194 ± 0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.000231 ± 3.8e-05</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 5e-06</t>
         </is>
@@ -2483,15 +3815,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2517,10 +3853,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>golinski</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>otl_circuit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>piston</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rastrigin_6d</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -2549,10 +3905,30 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>576 ± 3.9e-08</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>0.00608 ± 0.0012</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.000194 ± 1.4e-10</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.000256 ± 7.3e-10</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.97 ± 1.3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -2575,12 +3951,32 @@
           <t>27.9 ± 22</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>576 ± 5.2e-10</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>0.0056 ± 0.0018</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.000194 ± 2.7e-11</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.000256 ± 1.7e-09</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.24 ± 0.13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -2603,12 +3999,32 @@
           <t>22.8 ± 24</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>0.00788 ± 0.0068</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.000651 ± 0.00091</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>0.000195 ± 5.7e-05</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2.11 ± 2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.0121 ± 0.013</t>
         </is>
@@ -2631,12 +4047,32 @@
           <t>20.2 ± 22</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>0.00712 ± 0.0034</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>0.000194 ± 0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.000234 ± 5e-06</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>1.15 ± 0.079</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>0.00648 ± 0.0045</t>
         </is>
@@ -2665,10 +4101,30 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>605 ± 0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>0.0064 ± 2.5e-06</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.00121 ± 0.00064</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.000211 ± 3.9e-05</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.16 ± 0.044</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>0.00564 ± 1.7e-06</t>
         </is>
@@ -2693,10 +4149,30 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>576 ± 0.0015</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>0.00736 ± 0.0051</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.000474 ± 0.00034</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.000256 ± 5.3e-10</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.85 ± 1.5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.00814 ± 0.0075</t>
         </is>
@@ -2719,12 +4195,32 @@
           <t>21.7 ± 24</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>0.00584 ± 0.0043</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>0.000194 ± 0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.000241 ± 8.8e-06</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.14 ± 0.054</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>0.00746 ± 0.0063</t>
         </is>
@@ -2747,12 +4243,32 @@
           <t>11.4 ± 18</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>0.00624 ± 0.00086</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.000333 ± 0.00028</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>0.000197 ± 5.6e-05</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>1.11 ± 0.04</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 3.3e-06</t>
         </is>
@@ -2781,10 +4297,30 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>602 ± 6.2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>0.0064 ± 8.6e-10</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.000886 ± 3.6e-06</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>0.000159 ± 5.3e-05</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2.97 ± 2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>0.00564 ± 2.3e-07</t>
         </is>
@@ -2809,10 +4345,30 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>576 ± 3.9e-06</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>0.00572 ± 0.0033</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.000474 ± 0.00034</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.000233 ± 4.7e-05</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.28 ± 0.16</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -2835,12 +4391,32 @@
           <t>25 ± 26</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>0.00524 ± 0.0035</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>0.000194 ± 0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.000241 ± 8.8e-06</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1.97 ± 1.7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>0.00662 ± 0.0045</t>
         </is>
@@ -2863,12 +4439,32 @@
           <t>16.8 ± 21</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>0.0064 ± 5.1e-07</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.000235 ± 8.1e-05</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.000203 ± 3.6e-05</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>1.12 ± 0.043</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>0.00564 ± 3.5e-06</t>
         </is>
@@ -2897,10 +4493,30 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>576 ± 7.1e-06</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>0.00576 ± 0.0016</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.000474 ± 0.00034</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>0.000124 ± 5.3e-05</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1.3 ± 0.15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>0.00647 ± 0.0045</t>
         </is>
@@ -2923,12 +4539,32 @@
           <t>21.8 ± 23</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>0.00524 ± 0.0035</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>0.000194 ± 0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.000225 ± 3.5e-05</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>1.07 ± 0.077</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>0.00814 ± 0.0075</t>
         </is>
@@ -2951,12 +4587,32 @@
           <t>7.1 ± 15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>0.00576 ± 0.0016</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.000413 ± 0.00025</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.000142 ± 6.1e-05</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1.09 ± 0.041</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 2.8e-06</t>
         </is>
@@ -2985,10 +4641,30 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>576 ± 5.7e-06</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>0.00496 ± 0.0022</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.000375 ± 0.00027</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.000175 ± 7.4e-05</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1.12 ± 0.12</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>0.00564 ± 1.3e-06</t>
         </is>
@@ -3013,10 +4689,30 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
           <t>0.00428 ± 0.0037</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>0.000235 ± 8.1e-05</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.000199 ± 4.4e-05</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.17 ± 0.11</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 2.5e-06</t>
         </is>
@@ -3039,12 +4735,32 @@
           <t>4.64 ± 9.8</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>0.00445 ± 0.0037</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.000377 ± 0.00027</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>0.000137 ± 2.7e-05</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>1.1 ± 0.031</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>0.00564 ± 2.7e-06</t>
         </is>
@@ -3073,10 +4789,30 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>576 ± 0.74</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>0.00576 ± 0.0016</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.000194 ± 1.1e-11</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.000256 ± 6.6e-10</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1.26 ± 0.073</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>0.00647 ± 0.0045</t>
         </is>
@@ -3101,10 +4837,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>589 ± 25</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>0.00788 ± 0.0068</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.000651 ± 0.00091</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>0.000178 ± 5.2e-05</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.9 ± 1.4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>0.0102 ± 0.0092</t>
         </is>
@@ -3127,12 +4883,32 @@
           <t>2.34 ± 4.7</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>576 ± 0</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>0.00563 ± 0.0033</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>0.000194 ± 0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.000236 ± 6.2e-06</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>1.11 ± 0.044</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 2.5e-06</t>
         </is>
@@ -3157,7 +4933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3166,6 +4942,10 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3191,10 +4971,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>golinski</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>otl_circuit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>piston</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rastrigin_6d</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -3221,12 +5021,32 @@
           <t>0.344 ± 0.54</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3.58e-06 ± 1e-07</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>0.00381 ± 0.014</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.53e-06 ± 9.7e-07</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.000298 ± 0.00029</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.0339 ± 0.13</t>
         </is>
@@ -3251,10 +5071,30 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>1.71e-07 ± 1.4e-08</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.00794 ± 0.019</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>4.33e-07 ± 5.5e-07</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>1.23e-06 ± 9.1e-07</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.0343 ± 0.13</t>
         </is>
@@ -3277,12 +5117,32 @@
           <t>2.09 ± 3.3</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>0.0937 ± 0.11</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.00188 ± 0.0038</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00103 ± 0.00065</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.178 ± 0.34</t>
         </is>
@@ -3305,12 +5165,32 @@
           <t>1.11 ± 3.9</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>0.00409 ± 0.014</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3.07e-05 ± 6.1e-05</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.000695 ± 0.00033</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>0.0176 ± 0.091</t>
         </is>
@@ -3337,12 +5217,32 @@
           <t>0.571 ± 1.4</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>48.7 ± 30</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>0.000738 ± 0.0011</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.0248 ± 0.022</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00162 ± 0.00098</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>0.000135 ± 0.00025</t>
         </is>
@@ -3367,10 +5267,30 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>0.941 ± 1.9</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>0.0397 ± 0.075</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.00196 ± 0.0015</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>0.000571 ± 0.00054</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.0362 ± 0.13</t>
         </is>
@@ -3393,12 +5313,32 @@
           <t>0.736 ± 1.5</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>0.0251 ± 0.049</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>1.74e-05 ± 2.3e-05</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.000673 ± 0.00042</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>0.061 ± 0.19</t>
         </is>
@@ -3421,12 +5361,32 @@
           <t>0.273 ± 0.46</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>0.000797 ± 0.0019</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.0162 ± 0.011</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00172 ± 0.00088</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>0.00107 ± 0.0013</t>
         </is>
@@ -3453,12 +5413,32 @@
           <t>0.0884 ± 0.13</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>24.7 ± 26</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>3.12e-07 ± 3.7e-06</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.0571 ± 0.02</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.00331 ± 0.0033</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>7.81e-06 ± 3.4e-05</t>
         </is>
@@ -3483,10 +5463,30 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>0.000123 ± 0.00015</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>0.00649 ± 0.017</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.0122 ± 0.013</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.00173 ± 6.6e-06</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>0.0386 ± 0.13</t>
         </is>
@@ -3509,12 +5509,32 @@
           <t>1.19 ± 1.7</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>0.0281 ± 0.05</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>0.000411 ± 0.00051</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>0.00126 ± 0.00071</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>27.3 ± 0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>0.0343 ± 0.13</t>
         </is>
@@ -3537,12 +5557,32 @@
           <t>0.332 ± 0.54</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>0.000436 ± 0.00059</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.0222 ± 0.018</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.00258 ± 0.00082</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>9.86 ± 0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>0.00044 ± 0.00073</t>
         </is>
@@ -3571,10 +5611,30 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>3.75 ± 2.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>0.00432 ± 0.014</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.0272 ± 0.03</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.00359 ± 0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>0.000791 ± 0.0013</t>
         </is>
@@ -3597,12 +5657,32 @@
           <t>0.527 ± 1.1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>0.0261 ± 0.05</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>0.000213 ± 0.00035</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>0.00158 ± 0.00071</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>0.0471 ± 0.18</t>
         </is>
@@ -3625,12 +5705,32 @@
           <t>0.294 ± 0.54</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>0.000882 ± 0.0015</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0204 ± 0.017</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.00182 ± 0.00068</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>0.000907 ± 0.0011</t>
         </is>
@@ -3657,12 +5757,32 @@
           <t>0.424 ± 0.88</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.307 ± 0.61</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>0.0127 ± 0.022</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.0148 ± 0.012</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.00428 ± 0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>0.000224 ± 0.00067</t>
         </is>
@@ -3685,12 +5805,32 @@
           <t>0.523 ± 1.1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>0.0453 ± 0.063</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>0.000403 ± 0.0005</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>0.00244 ± 0.00092</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>0.0357 ± 0.13</t>
         </is>
@@ -3715,10 +5855,30 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>1.49 ± 3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>0.025 ± 0.026</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.0147 ± 0.013</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.00284 ± 0.0018</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>0.00284 ± 0.0053</t>
         </is>
@@ -3745,12 +5905,32 @@
           <t>0.00144 ± 0.0029</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>9.65 ± 6.6</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>0.00789 ± 0.019</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>6.33e-07 ± 4.8e-07</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>0.0178 ± 0.091</t>
         </is>
@@ -3775,10 +5955,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>72.8 ± 60</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>0.102 ± 0.13</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.00188 ± 0.0038</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.00107 ± 0.00069</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>0.195 ± 0.34</t>
         </is>
@@ -3801,12 +6001,32 @@
           <t>0.288 ± 1.1</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>29 ± 47</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>0.00431 ± 0.014</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.23e-05 ± 2.5e-05</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>0.000688 ± 0.00052</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>0.000752 ± 0.002</t>
         </is>
@@ -3831,15 +6051,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3865,10 +6089,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>golinski</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>otl_circuit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>piston</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rastrigin_6d</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -3895,12 +6139,32 @@
           <t>0.00407 ± 0.0032</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3.48e-06 ± 1.1e-07</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>0.00381 ± 0.014</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3.87e-06 ± 3.2e-06</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2.16e-07 ± 1.5e-07</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>29.2 ± 7.3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.0339 ± 0.13</t>
         </is>
@@ -3925,10 +6189,30 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>1.72e-07 ± 1.8e-09</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.0097 ± 0.021</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4.64e-07 ± 3.8e-07</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4.6e-07 ± 5.1e-07</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25.1 ± 5.7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.034 ± 0.13</t>
         </is>
@@ -3951,12 +6235,32 @@
           <t>2.34 ± 3.4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>0.0784 ± 0.1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.00188 ± 0.0038</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00098 ± 0.00066</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>19.2 ± 11</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.207 ± 0.34</t>
         </is>
@@ -3979,12 +6283,32 @@
           <t>1.77 ± 4.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>0.019 ± 0.064</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00102 ± 0.00023</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>6.53 ± 4.3</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>0.0193 ± 0.1</t>
         </is>
@@ -4011,12 +6335,32 @@
           <t>0.139 ± 0.74</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>72.5 ± 0</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>0.000902 ± 0.0012</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.056 ± 0.029</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00122 ± 0.00051</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20.7 ± 6.8</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>0.000115 ± 0.00017</t>
         </is>
@@ -4041,10 +6385,30 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>1.37 ± 2.6</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>0.0436 ± 0.085</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.00586 ± 0.0099</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2.93e-05 ± 3.7e-05</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>23.5 ± 3.1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.0513 ± 0.15</t>
         </is>
@@ -4067,12 +6431,32 @@
           <t>1.72 ± 2.2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>0.0343 ± 0.064</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>6.94e-05 ± 7e-05</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.000517 ± 0.00037</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13.7 ± 3.8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>0.0702 ± 0.2</t>
         </is>
@@ -4095,12 +6479,32 @@
           <t>0.854 ± 3.3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>0.00234 ± 0.01</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.0159 ± 0.011</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00119 ± 0.0011</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>3.88 ± 2.8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>0.000646 ± 0.0023</t>
         </is>
@@ -4127,12 +6531,32 @@
           <t>0.00449 ± 0.0035</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>62.9 ± 19</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>-6.55e-07 ± 4.2e-07</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.0666 ± 0.03</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0024 ± 0.002</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>32.5 ± 11</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1.67e-06 ± 5.6e-06</t>
         </is>
@@ -4157,10 +6581,30 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>6.77e-05 ± 8.2e-05</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>0.0218 ± 0.049</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.0124 ± 0.014</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.00106 ± 0.00057</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>31.4 ± 2.6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>0.0341 ± 0.13</t>
         </is>
@@ -4183,12 +6627,32 @@
           <t>1.81 ± 2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>0.0278 ± 0.05</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>3.07e-05 ± 6.1e-05</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>0.00099 ± 0.00074</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13.1 ± 9.6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>0.0467 ± 0.18</t>
         </is>
@@ -4211,12 +6675,32 @@
           <t>0.765 ± 1.3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>0.000174 ± 0.00025</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.0163 ± 0.014</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.002 ± 0.00056</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>3.91 ± 2.2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>0.000521 ± 0.00094</t>
         </is>
@@ -4243,12 +6727,32 @@
           <t>0.17 ± 0.79</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7.82 ± 4.1</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>0.00804 ± 0.019</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.0119 ± 0.013</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.00323 ± 0.0018</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30.6 ± 5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>0.0171 ± 0.091</t>
         </is>
@@ -4271,12 +6775,32 @@
           <t>1.29 ± 1.8</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>0.0277 ± 0.05</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>3.07e-05 ± 6.1e-05</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>0.000791 ± 0.00055</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9.43 ± 2.5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>0.0511 ± 0.15</t>
         </is>
@@ -4299,12 +6823,32 @@
           <t>0.0895 ± 0.19</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>0.00886 ± 0.02</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0157 ± 0.013</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.00249 ± 0.00091</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>4.79 ± 1.6</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>0.000347 ± 0.00085</t>
         </is>
@@ -4331,12 +6875,32 @@
           <t>0.00777 ± 0.022</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.965 ± 1.4</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>0.018 ± 0.026</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.00408 ± 0.0075</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>0.00165 ± 0.0013</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>24.3 ± 5.9</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>6.35e-05 ± 0.00015</t>
         </is>
@@ -4359,12 +6923,32 @@
           <t>1.42 ± 2.1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>0.0392 ± 0.049</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>0.000202 ± 0.00037</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.00203 ± 0.00067</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12.7 ± 3.5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>0.000237 ± 0.00042</t>
         </is>
@@ -4387,12 +6971,32 @@
           <t>0.159 ± 0.47</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>0.0387 ± 0.05</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.0289 ± 0.017</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.00226 ± 0.00077</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>3.96 ± 2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>0.000346 ± 0.00088</t>
         </is>
@@ -4421,10 +7025,30 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>2.72 ± 2.4</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
           <t>0.00786 ± 0.019</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2.74e-07 ± 1.7e-07</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>4.57e-07 ± 5.5e-07</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20.7 ± 4.5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>0.017 ± 0.091</t>
         </is>
@@ -4449,10 +7073,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>28.8 ± 51</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>0.0783 ± 0.1</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.00188 ± 0.0038</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.00115 ± 0.00057</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>21.2 ± 8.6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>0.173 ± 0.3</t>
         </is>
@@ -4477,10 +7121,30 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>10.6 ± 4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>0.0403 ± 0.1</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.000695 ± 0.00033</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>5.2 ± 2.6</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>0.00022 ± 0.00055</t>
         </is>

--- a/benchmark/notebooks/acq_method_tables.xlsx
+++ b/benchmark/notebooks/acq_method_tables.xlsx
@@ -461,19 +461,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,40 +490,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ackley_10d</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>ackley_2d</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>branin_hetero</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>golinski</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>otl_circuit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>piston</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>rastrigin_6d</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -539,42 +545,47 @@
           <t>Standard LVGP</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>0.00641 ± 0.0063</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>0.0911 ± 0.057</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>2.56e-06 ± 8.5e-08</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>0.00413 ± 0.015</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>1.53e-06 ± 9.7e-07</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.000307 ± 0.00029</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t>23.5 ± 8.7</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.0322 ± 0.12</t>
         </is>
@@ -589,40 +600,45 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>0.0302 ± 0.035</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>0.0913 ± 0.057</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1.24e-07 ± 1e-08</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.00858 ± 0.021</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>4.33e-07 ± 5.5e-07</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>1.24e-06 ± 9.2e-07</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>1.49e-06 ± 1.5e-06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>22.7 ± 6.9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.0326 ± 0.12</t>
         </is>
@@ -637,40 +653,45 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>0.624 ± 1.2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>0.649 ± 1.1</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.0912 ± 0.1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.00142 ± 0.0028</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.0011 ± 0.0007</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>18.9 ± 8.3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.172 ± 0.33</t>
         </is>
@@ -685,40 +706,45 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>0.196 ± 0.71</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>0.0516 ± 0.088</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.00441 ± 0.015</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>3.07e-05 ± 6.1e-05</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.000715 ± 0.00033</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>7.57 ± 4.4</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>0.0168 ± 0.087</t>
         </is>
@@ -735,42 +761,47 @@
           <t>Standard LVGP</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>0.0127 ± 0.015</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>0.0697 ± 0.057</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>31.6 ± 17</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>0.000736 ± 0.0011</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.0242 ± 0.022</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>0.00168 ± 0.001</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11.6 ± 3.7</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>0.000135 ± 0.00025</t>
         </is>
@@ -785,40 +816,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>0.547 ± 1.2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>0.289 ± 0.91</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>0.941 ± 1.9</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>0.0395 ± 0.072</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.00164 ± 0.0012</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>0.000571 ± 0.00054</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>0.000361 ± 0.0004</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>19.1 ± 2.4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.0345 ± 0.12</t>
         </is>
@@ -833,40 +869,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>0.12 ± 0.55</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.179 ± 0.42</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>0.026 ± 0.048</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>1.74e-05 ± 2.3e-05</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>0.000718 ± 0.00046</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>17.2 ± 6.5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.06 ± 0.18</t>
         </is>
@@ -881,40 +922,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>0.0145 ± 0.012</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>0.0736 ± 0.088</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>0.000795 ± 0.0019</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>0.0155 ± 0.011</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>0.00177 ± 0.00093</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>4.18 ± 3.2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.00107 ± 0.0013</t>
         </is>
@@ -931,42 +977,47 @@
           <t>Standard LVGP</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>0.0123 ± 0.012</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>0.0532 ± 0.054</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>16.3 ± 17</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>3.11e-07 ± 3.7e-06</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>0.0565 ± 0.02</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>0.00339 ± 0.0033</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19.5 ± 12</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>7.92e-06 ± 3.3e-05</t>
         </is>
@@ -981,40 +1032,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>0.0212 ± 0.024</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>0.092 ± 0.049</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>0.000119 ± 0.00015</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>0.00697 ± 0.019</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>0.0119 ± 0.013</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.00174 ± 4e-06</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.00182 ± 0.0015</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>24.4 ± 8.1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>0.0369 ± 0.12</t>
         </is>
@@ -1029,40 +1085,45 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>0.221 ± 0.76</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>0.419 ± 0.71</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>0.0292 ± 0.049</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>0.00033 ± 0.00041</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>0.00131 ± 0.00074</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>23.6 ± 0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>15.1 ± 8.4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>0.0326 ± 0.12</t>
         </is>
@@ -1077,40 +1138,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>0.0132 ± 0.014</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>0.0898 ± 0.092</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>0.000435 ± 0.00059</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>0.0218 ± 0.018</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>0.00267 ± 0.00088</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>9.81 ± 0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>5.61 ± 3.9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>0.000441 ± 0.00073</t>
         </is>
@@ -1129,40 +1195,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>0.0166 ± 0.016</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>0.0862 ± 0.054</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>3.75 ± 2.1</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>0.00464 ± 0.016</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>0.0268 ± 0.029</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.00378 ± 0</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+          <t>0.00197 ± 0.0013</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>28.1 ± 8.4</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>0.000791 ± 0.0013</t>
         </is>
@@ -1177,40 +1248,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>0.217 ± 0.77</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>0.0966 ± 0.12</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>0.0271 ± 0.049</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>0.000173 ± 0.00028</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>0.00163 ± 0.00073</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>9.95 ± 3.9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>0.0462 ± 0.18</t>
         </is>
@@ -1223,42 +1299,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>0.0122 ± 0.012</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>0.0842 ± 0.088</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>0.00088 ± 0.0015</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>0.0203 ± 0.017</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>0.00189 ± 0.00073</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>4.92 ± 1.7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>0.000906 ± 0.0011</t>
         </is>
@@ -1277,40 +1358,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>0.024 ± 0.025</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>0.078 ± 0.085</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>0.307 ± 0.61</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>0.0137 ± 0.024</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>0.0147 ± 0.012</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.00448 ± 0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>0.00246 ± 0.0012</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>26.3 ± 5.6</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>0.000224 ± 0.00067</t>
         </is>
@@ -1325,40 +1411,45 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>0.027 ± 0.027</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>0.19 ± 0.39</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>0.0467 ± 0.061</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>0.000322 ± 0.0004</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>0.00254 ± 0.00099</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>11.2 ± 4.1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>0.0341 ± 0.12</t>
         </is>
@@ -1371,42 +1462,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>0.0191 ± 0.024</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>0.131 ± 0.41</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>1.49 ± 3</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>0.0267 ± 0.029</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>0.0146 ± 0.013</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>0.00295 ± 0.0018</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>7.34 ± 5.3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>0.00284 ± 0.0053</t>
         </is>
@@ -1423,42 +1519,47 @@
           <t>Heteroscedastic LVGP</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>0.0264 ± 0.024</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>0.00249 ± 0.0073</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>9.65 ± 6.6</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>0.00853 ± 0.021</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>6.33e-07 ± 4.8e-07</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>1.71e-06 ± 3e-06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>22.4 ± 8.3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>0.017 ± 0.087</t>
         </is>
@@ -1473,40 +1574,45 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>0.723 ± 1.3</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>0.377 ± 0.91</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>56.7 ± 47</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>0.1 ± 0.12</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>0.00142 ± 0.0028</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>0.00112 ± 0.00073</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>20.1 ± 10</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>0.188 ± 0.33</t>
         </is>
@@ -1521,40 +1627,45 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>0.11 ± 0.55</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>0.0269 ± 0.081</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>20 ± 29</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>0.00463 ± 0.015</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>1.23e-05 ± 2.5e-05</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>0.000713 ± 0.00054</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>8.7 ± 4.2</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>0.000752 ± 0.002</t>
         </is>
@@ -1579,19 +1690,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1607,40 +1719,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ackley_10d</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>ackley_2d</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>branin_hetero</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>golinski</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>otl_circuit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>piston</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>rastrigin_6d</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -1657,42 +1774,47 @@
           <t>Standard LVGP</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>0.00408 ± 0.0047</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>0.00124 ± 0.0059</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>2.5e-06 ± 8.5e-08</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>0.00413 ± 0.015</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>3.87e-06 ± 3.2e-06</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>2.16e-07 ± 1.5e-07</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>28.3 ± 6.1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.0322 ± 0.12</t>
         </is>
@@ -1707,40 +1829,45 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>0.0188 ± 0.021</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>0.0993 ± 0.063</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1.26e-07 ± 1.3e-09</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.0105 ± 0.023</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>4.64e-07 ± 3.8e-07</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>4.62e-07 ± 5.1e-07</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>25 ± 5.7</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.0323 ± 0.12</t>
         </is>
@@ -1755,40 +1882,45 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>1.39 ± 0.68</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>0.726 ± 1.3</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>0.529 ± 0.88</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.0769 ± 0.094</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.00142 ± 0.0028</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.00104 ± 0.00071</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>18.2 ± 9.6</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.2 ± 0.33</t>
         </is>
@@ -1801,42 +1933,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>1.25 ± 0.19</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.294 ± 0.88</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>0.0941 ± 0.12</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.0183 ± 0.06</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.00105 ± 0.00023</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>6.49 ± 4.2</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>0.0185 ± 0.098</t>
         </is>
@@ -1855,40 +1992,45 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>0.0131 ± 0.014</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>0.00462 ± 0.023</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>43.8 ± 0</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>0.0009 ± 0.0012</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.055 ± 0.03</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>0.00127 ± 0.00052</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>20.7 ± 6.8</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>0.000114 ± 0.00017</t>
         </is>
@@ -1903,40 +2045,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>0.28 ± 1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>0.238 ± 0.59</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>1.37 ± 2.6</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>0.0426 ± 0.081</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.00558 ± 0.0096</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>2.93e-05 ± 3.7e-05</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>23.4 ± 3.2</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.0488 ± 0.15</t>
         </is>
@@ -1951,40 +2098,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>1.75 ± 0.94</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>0.709 ± 1.3</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.238 ± 0.59</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>0.0349 ± 0.062</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>6.94e-05 ± 7e-05</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>0.000532 ± 0.00038</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>13.6 ± 3.8</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.0684 ± 0.19</t>
         </is>
@@ -1997,42 +2149,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>4.44e-16 ± 0</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>0.00491 ± 0.006</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>0.0548 ± 0.066</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>0.0025 ± 0.011</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>0.0158 ± 0.011</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>0.00125 ± 0.0011</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>3.87 ± 2.8</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.000646 ± 0.0023</t>
         </is>
@@ -2051,40 +2208,45 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>0.0102 ± 0.0098</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>0.00181 ± 0.0076</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>37.3 ± 13</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>-6.54e-07 ± 4.2e-07</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>0.0659 ± 0.03</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>0.0025 ± 0.0021</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>30.6 ± 9.4</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>1.81e-06 ± 5.8e-06</t>
         </is>
@@ -2099,40 +2261,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>0.022 ± 0.031</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>0.0802 ± 0.058</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>6.39e-05 ± 7.9e-05</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>0.0225 ± 0.048</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>0.0121 ± 0.014</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>0.00109 ± 0.0006</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>31.2 ± 2.5</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0.0324 ± 0.12</t>
         </is>
@@ -2147,40 +2314,45 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>1.75 ± 0.93</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>0.422 ± 1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>0.662 ± 0.95</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>0.029 ± 0.049</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>3.07e-05 ± 6.1e-05</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>0.001 ± 0.00074</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>12.2 ± 8</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0.0457 ± 0.18</t>
         </is>
@@ -2193,42 +2365,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>4.44e-16 ± 0</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 0.0092</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>0.158 ± 0.39</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>0.000174 ± 0.00025</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>0.0163 ± 0.014</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>0.00205 ± 0.00054</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>3.89 ± 2.2</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0.000521 ± 0.00094</t>
         </is>
@@ -2247,40 +2424,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>0.0259 ± 0.023</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>0.0211 ± 0.035</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>7.82 ± 4.1</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>0.00868 ± 0.021</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>0.0117 ± 0.013</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>0.00336 ± 0.0018</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>30.4 ± 4.9</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0.0163 ± 0.087</t>
         </is>
@@ -2295,40 +2477,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>2.4 ± 0.41</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>0.425 ± 1</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>0.434 ± 0.74</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>0.0288 ± 0.049</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>3.07e-05 ± 6.1e-05</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>0.000822 ± 0.00057</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>9.46 ± 2.4</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0.0486 ± 0.15</t>
         </is>
@@ -2341,42 +2528,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>4.44e-16 ± 0</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>0.00801 ± 0.0085</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>0.0421 ± 0.048</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>0.0095 ± 0.021</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>0.0155 ± 0.013</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>0.0026 ± 0.00096</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>4.8 ± 1.6</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>0.000346 ± 0.00085</t>
         </is>
@@ -2395,40 +2587,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>0.0208 ± 0.019</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>0.00541 ± 0.014</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>0.965 ± 1.4</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>0.0194 ± 0.028</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>0.0039 ± 0.0073</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>0.00173 ± 0.0013</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>24.3 ± 5.9</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>6.35e-05 ± 0.00015</t>
         </is>
@@ -2443,40 +2640,45 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>3.13 ± 1.2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>0.116 ± 0.55</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>0.666 ± 1.1</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>0.0413 ± 0.048</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>0.000162 ± 0.00029</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>0.00209 ± 0.0007</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>12.6 ± 3.4</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0.000237 ± 0.00041</t>
         </is>
@@ -2491,40 +2693,45 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>1.93 ± 0.23</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
           <t>0.00552 ± 0.0094</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>0.135 ± 0.41</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>0.0406 ± 0.049</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>0.0287 ± 0.017</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>0.00238 ± 0.0008</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>3.95 ± 2</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>0.000346 ± 0.00089</t>
         </is>
@@ -2541,42 +2748,47 @@
           <t>Heteroscedastic LVGP</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>0.0203 ± 0.025</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>0.00189 ± 0.0049</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2.44 ± 2.5</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>0.0085 ± 0.021</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>2.74e-07 ± 1.7e-07</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>4.58e-07 ± 5.5e-07</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>20.5 ± 4.5</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>0.0162 ± 0.087</t>
         </is>
@@ -2591,40 +2803,45 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>1.72 ± 1.1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>0.723 ± 1.3</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>0.288 ± 0.78</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>17.5 ± 28</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>0.0768 ± 0.094</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>0.00142 ± 0.0028</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>0.00123 ± 0.00062</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>20.4 ± 7.4</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>0.168 ± 0.3</t>
         </is>
@@ -2637,42 +2854,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>0.398 ± 0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>0.397 ± 1</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>0.154 ± 0.57</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>10.6 ± 4</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>0.0411 ± 0.1</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>0.000715 ± 0.00033</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>5.19 ± 2.6</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>0.000219 ± 0.00055</t>
         </is>
@@ -2697,19 +2919,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2725,40 +2948,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ackley_10d</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>ackley_2d</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>branin_hetero</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>golinski</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>otl_circuit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>piston</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>rastrigin_6d</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -2775,42 +3003,47 @@
           <t>Standard LVGP</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>0.01 ± 5.3e-08</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>23.8 ± 22</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>576 ± 3.9e-08</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.00608 ± 0.0012</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.000194 ± 5.3e-11</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.000247 ± 7.7e-06</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t>1.28 ± 0.12</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -2825,40 +3058,45 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>0.01 ± 9e-07</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>26.6 ± 22</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>576 ± 4.9e-09</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>0.00576 ± 0.0016</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.000194 ± 1.7e-11</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.000256 ± 8.5e-09</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000256 ± 7.3e-09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>1.29 ± 0.12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -2873,40 +3111,45 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>0.016 ± 0.012</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>23.7 ± 27</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.00892 ± 0.0073</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.000651 ± 0.00091</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>0.000183 ± 5.8e-05</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>2.68 ± 1.9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.0122 ± 0.015</t>
         </is>
@@ -2921,40 +3164,45 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>0.0111 ± 0.0054</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>10.8 ± 19</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.00608 ± 0.0012</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>0.000194 ± 0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.000236 ± 6.2e-06</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>1.13 ± 0.044</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>0.00647 ± 0.0045</t>
         </is>
@@ -2973,40 +3221,45 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>0.01 ± 2.2e-07</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>12 ± 19</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>597 ± 19</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>0.0064 ± 2.3e-06</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.000753 ± 0.00028</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>0.000196 ± 5e-05</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>1.13 ± 0.089</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>0.00564 ± 1.8e-06</t>
         </is>
@@ -3021,40 +3274,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>0.0118 ± 0.0059</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>24.7 ± 24</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>576 ± 4e-05</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>0.0066 ± 0.0048</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.000514 ± 0.00032</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.000256 ± 2.3e-10</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000256 ± 4.3e-09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>1.26 ± 0.1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -3069,40 +3327,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>0.011 ± 0.0054</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>12.9 ± 19</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>0.00556 ± 0.0034</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>0.000194 ± 0</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>0.00021 ± 4.2e-05</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>1.87 ± 1.5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.00663 ± 0.0045</t>
         </is>
@@ -3115,42 +3378,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 1.7e-07</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>15.9 ± 21</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>0.0064 ± 3.9e-06</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>0.000908 ± 0.0008</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>0.000202 ± 6.4e-05</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>1.15 ± 0.091</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.00564 ± 5.3e-06</t>
         </is>
@@ -3167,42 +3435,47 @@
           <t>Standard LVGP</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 1.5e-07</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>10.4 ± 18</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>584 ± 11</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>0.0064 ± 7.5e-09</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>0.00079 ± 0.0002</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>0.000175 ± 3.7e-05</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>1.95 ± 1.5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>0.00564 ± 4.8e-07</t>
         </is>
@@ -3217,40 +3490,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>0.01 ± 5.4e-07</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>23.4 ± 22</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>576 ± 4e-06</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>0.00592 ± 0.0014</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>0.000514 ± 0.00032</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.000245 ± 1.1e-05</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000223 ± 5.7e-05</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>1.24 ± 0.089</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -3265,40 +3543,45 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>0.012 ± 0.0075</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>14.2 ± 18</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>0.00524 ± 0.0035</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>0.000275 ± 9.9e-05</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>0.000209 ± 5.3e-05</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4.72 ± 0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2.49 ± 1.7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -3313,40 +3596,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>0.01 ± 1.8e-07</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>17.3 ± 21</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>0.0064 ± 1.2e-06</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>0.000514 ± 0.00032</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>0.000173 ± 6.4e-05</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>1.15 ± 0</t>
-        </is>
-      </c>
       <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>1.11 ± 0.037</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 3.5e-06</t>
         </is>
@@ -3365,40 +3653,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>0.01 ± 2.7e-07</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>25 ± 22</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>576 ± 9.1e-06</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>0.00608 ± 0.0012</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>0.000512 ± 0.00032</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>6.4e-05 ± 0</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+          <t>0.000185 ± 7.3e-05</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.3 ± 0.21</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 4.8e-06</t>
         </is>
@@ -3413,40 +3706,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>0.012 ± 0.0075</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>16.4 ± 21</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>0.0054 ± 0.0034</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>0.000235 ± 8.1e-05</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>0.000211 ± 3.7e-05</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>1.19 ± 0.1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>0.00662 ± 0.0045</t>
         </is>
@@ -3459,42 +3757,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 1.5e-07</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>14.9 ± 21</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>0.0064 ± 3.1e-06</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>0.000275 ± 0.0001</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>0.000185 ± 6.9e-05</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>1.11 ± 0.054</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>0.00564 ± 5.1e-06</t>
         </is>
@@ -3513,40 +3816,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>0.01 ± 4.8e-07</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>15.1 ± 21</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>576 ± 0.00033</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>0.00544 ± 0.0019</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>0.000275 ± 9.9e-05</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>5.89e-05 ± 0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>0.00015 ± 6.6e-05</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>1.09 ± 0.041</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 2.3e-06</t>
         </is>
@@ -3561,40 +3869,45 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>0.01 ± 6.2e-07</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>13.6 ± 21</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>0.00505 ± 0.0045</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>0.000275 ± 9.9e-05</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>0.000161 ± 7.4e-05</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>1.11 ± 0.048</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -3607,42 +3920,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 6e-07</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>9.12 ± 17</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>0.00465 ± 0.0023</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>0.000333 ± 0.00028</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>0.000153 ± 5.9e-05</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>1.1 ± 0.027</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>0.00564 ± 7.5e-06</t>
         </is>
@@ -3659,42 +3977,47 @@
           <t>Heteroscedastic LVGP</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 5.1e-07</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>1.41 ± 0.0085</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>576 ± 2.9e-06</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>0.00576 ± 0.0016</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>0.000194 ± 2.8e-11</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000256 ± 2.4e-08</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>1.25 ± 0.1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>0.00647 ± 0.0045</t>
         </is>
@@ -3709,40 +4032,45 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>0.017 ± 0.013</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>7.48 ± 18</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>592 ± 26</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>0.00839 ± 0.0071</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>0.000651 ± 0.00091</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>0.000198 ± 5.8e-05</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2.69 ± 1.9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>0.0131 ± 0.016</t>
         </is>
@@ -3757,40 +4085,45 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>0.011 ± 0.0054</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>4.5 ± 12</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>587 ± 22</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>0.00608 ± 0.0012</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>0.000194 ± 0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>0.000231 ± 3.8e-05</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>1.18 ± 0.088</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 5e-06</t>
         </is>
@@ -3815,19 +4148,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3843,40 +4177,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ackley_10d</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>ackley_2d</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>branin_hetero</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>golinski</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>otl_circuit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>piston</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>rastrigin_6d</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -3893,42 +4232,47 @@
           <t>Standard LVGP</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>0.01 ± 2.6e-08</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>1.41 ± 0.0058</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>576 ± 3.9e-08</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.00608 ± 0.0012</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.000194 ± 1.4e-10</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.000256 ± 7.3e-10</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>1.97 ± 1.3</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -3943,40 +4287,45 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>0.01 ± 4.1e-07</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>27.9 ± 22</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>576 ± 5.2e-10</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>0.0056 ± 0.0018</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.000194 ± 2.7e-11</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>0.000256 ± 1.7e-09</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>1.24 ± 0.13</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -3989,42 +4338,47 @@
           <t>Separate GP</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>0.0301 ± 0.015</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.017 ± 0.013</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>22.8 ± 24</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.00788 ± 0.0068</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.000651 ± 0.00091</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>0.000195 ± 5.7e-05</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>2.11 ± 2</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.0121 ± 0.013</t>
         </is>
@@ -4039,40 +4393,45 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.0464 ± 0.002</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>0.0121 ± 0.0075</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>20.2 ± 22</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.00712 ± 0.0034</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>0.000194 ± 0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.000234 ± 5e-06</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>1.15 ± 0.079</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>0.00648 ± 0.0045</t>
         </is>
@@ -4091,40 +4450,45 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>0.01 ± 1.9e-07</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2.89 ± 8</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>605 ± 0</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>0.0064 ± 2.5e-06</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.00121 ± 0.00064</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>0.000211 ± 3.9e-05</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>1.16 ± 0.044</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0.00564 ± 1.7e-06</t>
         </is>
@@ -4139,40 +4503,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>0.0115 ± 0.0059</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>16 ± 22</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>576 ± 0.0015</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>0.00736 ± 0.0051</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.000474 ± 0.00034</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>0.000256 ± 5.3e-10</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>1.85 ± 1.5</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.00814 ± 0.0075</t>
         </is>
@@ -4185,42 +4554,47 @@
           <t>Separate GP</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>0.0309 ± 0.016</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>0.0161 ± 0.012</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>21.7 ± 24</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>0.00584 ± 0.0043</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>0.000194 ± 0</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>0.000241 ± 8.8e-06</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>1.14 ± 0.054</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.00746 ± 0.0063</t>
         </is>
@@ -4233,42 +4607,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.04 ± 0</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 4.3e-08</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>11.4 ± 18</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>0.00624 ± 0.00086</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>0.000333 ± 0.00028</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>0.000197 ± 5.6e-05</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>1.11 ± 0.04</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 3.3e-06</t>
         </is>
@@ -4287,40 +4666,45 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>0.01 ± 1.3e-07</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>1.41 ± 0.0072</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>602 ± 6.2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>0.0064 ± 8.6e-10</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>0.000886 ± 3.6e-06</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>0.000159 ± 5.3e-05</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2.97 ± 2</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0.00564 ± 2.3e-07</t>
         </is>
@@ -4335,40 +4719,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>0.01 ± 9.3e-07</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>20.9 ± 22</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>576 ± 3.9e-06</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>0.00572 ± 0.0033</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>0.000474 ± 0.00034</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>0.000233 ± 4.7e-05</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>1.28 ± 0.16</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0.00731 ± 0.0062</t>
         </is>
@@ -4381,42 +4770,47 @@
           <t>Separate GP</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>0.0311 ± 0.016</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>0.014 ± 0.01</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>25 ± 26</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>0.00524 ± 0.0035</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>0.000194 ± 0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>0.000241 ± 8.8e-06</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>1.97 ± 1.7</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0.00662 ± 0.0045</t>
         </is>
@@ -4429,42 +4823,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.04 ± 0</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 9.3e-08</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>16.8 ± 21</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>0.0064 ± 5.1e-07</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>0.000235 ± 8.1e-05</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>0.000203 ± 3.6e-05</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>1.12 ± 0.043</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>0.00564 ± 3.5e-06</t>
         </is>
@@ -4483,40 +4882,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>0.01 ± 4.7e-07</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>2.83 ± 7.7</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>576 ± 7.1e-06</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>0.00576 ± 0.0016</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>0.000474 ± 0.00034</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>0.000124 ± 5.3e-05</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>1.3 ± 0.15</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0.00647 ± 0.0045</t>
         </is>
@@ -4529,42 +4933,47 @@
           <t>Separate GP</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>0.0328 ± 0.017</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>0.014 ± 0.01</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>21.8 ± 23</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>0.00524 ± 0.0035</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>0.000194 ± 0</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>0.000225 ± 3.5e-05</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>1.07 ± 0.077</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0.00814 ± 0.0075</t>
         </is>
@@ -4577,42 +4986,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.04 ± 0</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 7.3e-08</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>7.1 ± 15</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>0.00576 ± 0.0016</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>0.000413 ± 0.00025</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>0.000142 ± 6.1e-05</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>1.09 ± 0.041</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 2.8e-06</t>
         </is>
@@ -4631,40 +5045,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>0.01 ± 3.2e-07</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>1.41 ± 0.013</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>576 ± 5.7e-06</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>0.00496 ± 0.0022</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>0.000375 ± 0.00027</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>0.000175 ± 7.4e-05</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>1.12 ± 0.12</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>0.00564 ± 1.3e-06</t>
         </is>
@@ -4677,42 +5096,47 @@
           <t>Separate GP</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>0.0321 ± 0.026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>0.011 ± 0.0054</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>12.1 ± 22</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>0.00428 ± 0.0037</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>0.000235 ± 8.1e-05</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>0.000199 ± 4.4e-05</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>1.17 ± 0.11</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 2.5e-06</t>
         </is>
@@ -4725,42 +5149,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.0459 ± 0.0012</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 9e-08</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>4.64 ± 9.8</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>0.00445 ± 0.0037</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>0.000377 ± 0.00027</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>0.000137 ± 2.7e-05</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>1.1 ± 0.031</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>0.00564 ± 2.7e-06</t>
         </is>
@@ -4777,42 +5206,47 @@
           <t>Heteroscedastic LVGP</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 5.5e-07</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>1.41 ± 0.0073</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>576 ± 0.74</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>0.00576 ± 0.0016</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>0.000194 ± 1.1e-11</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>0.000256 ± 6.6e-10</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>1.26 ± 0.073</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>0.00647 ± 0.0045</t>
         </is>
@@ -4827,40 +5261,45 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>0.049 ± 0.047</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>0.017 ± 0.013</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>3.41 ± 9.6</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>589 ± 25</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>0.00788 ± 0.0068</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>0.000651 ± 0.00091</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>0.000178 ± 5.2e-05</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>1.9 ± 1.4</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>0.0102 ± 0.0092</t>
         </is>
@@ -4873,42 +5312,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>0.0415 ± 0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>0.0131 ± 0.009</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>2.34 ± 4.7</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>576 ± 0</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>0.00563 ± 0.0033</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>0.000194 ± 0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>0.000236 ± 6.2e-06</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>1.11 ± 0.044</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>0.00564 ± 2.5e-06</t>
         </is>
@@ -4933,19 +5377,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4961,40 +5406,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ackley_10d</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>ackley_2d</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>branin_hetero</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>golinski</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>otl_circuit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>piston</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>rastrigin_6d</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -5011,42 +5461,47 @@
           <t>Standard LVGP</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>0.00641 ± 0.0063</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>0.344 ± 0.54</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>3.58e-06 ± 1e-07</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>0.00381 ± 0.014</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>1.53e-06 ± 9.7e-07</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.000298 ± 0.00029</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t>23.7 ± 8.8</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.0339 ± 0.13</t>
         </is>
@@ -5061,40 +5516,45 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>0.0302 ± 0.035</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>0.793 ± 1.1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1.71e-07 ± 1.4e-08</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.00794 ± 0.019</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>4.33e-07 ± 5.5e-07</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>1.23e-06 ± 9.1e-07</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>1.48e-06 ± 1.5e-06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>22.9 ± 7</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.0343 ± 0.13</t>
         </is>
@@ -5109,40 +5569,45 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>0.63 ± 1.2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2.09 ± 3.3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.0937 ± 0.11</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.00188 ± 0.0038</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.00103 ± 0.00065</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>20.4 ± 10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.178 ± 0.34</t>
         </is>
@@ -5157,40 +5622,45 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>0.197 ± 0.71</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.11 ± 3.9</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.00409 ± 0.014</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>3.07e-05 ± 6.1e-05</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.000695 ± 0.00033</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>7.61 ± 4.4</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>0.0176 ± 0.091</t>
         </is>
@@ -5207,42 +5677,47 @@
           <t>Standard LVGP</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>0.0127 ± 0.015</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>0.571 ± 1.4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>48.7 ± 30</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>0.000738 ± 0.0011</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.0248 ± 0.022</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>0.00162 ± 0.00098</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11.6 ± 3.8</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>0.000135 ± 0.00025</t>
         </is>
@@ -5257,40 +5732,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>0.549 ± 1.2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2.53 ± 4.5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>0.941 ± 1.9</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>0.0397 ± 0.075</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.00196 ± 0.0015</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>0.000571 ± 0.00054</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>0.000361 ± 0.0004</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>19.3 ± 2.4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.0362 ± 0.13</t>
         </is>
@@ -5305,40 +5785,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>0.121 ± 0.56</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.736 ± 1.5</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>0.0251 ± 0.049</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>1.74e-05 ± 2.3e-05</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>0.000673 ± 0.00042</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>18 ± 7.8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.061 ± 0.19</t>
         </is>
@@ -5353,40 +5838,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>0.0145 ± 0.012</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>0.273 ± 0.46</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>0.000797 ± 0.0019</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>0.0162 ± 0.011</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>0.00172 ± 0.00088</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>4.23 ± 3.3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.00107 ± 0.0013</t>
         </is>
@@ -5403,42 +5893,47 @@
           <t>Standard LVGP</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>0.0123 ± 0.012</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>0.0884 ± 0.13</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>24.7 ± 26</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>3.12e-07 ± 3.7e-06</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>0.0571 ± 0.02</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>0.00331 ± 0.0033</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>20.3 ± 14</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>7.81e-06 ± 3.4e-05</t>
         </is>
@@ -5453,40 +5948,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>0.0212 ± 0.024</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>0.516 ± 1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>0.000123 ± 0.00015</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>0.00649 ± 0.017</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>0.0122 ± 0.013</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.00173 ± 6.6e-06</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.00179 ± 0.0014</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>24.6 ± 8.1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>0.0386 ± 0.13</t>
         </is>
@@ -5501,40 +6001,45 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>0.223 ± 0.77</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>1.19 ± 1.7</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>0.0281 ± 0.05</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>0.000411 ± 0.00051</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>0.00126 ± 0.00071</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>27.3 ± 0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>16.5 ± 10</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>0.0343 ± 0.13</t>
         </is>
@@ -5549,40 +6054,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>0.0132 ± 0.014</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>0.332 ± 0.54</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>0.000436 ± 0.00059</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>0.0222 ± 0.018</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>0.00258 ± 0.00082</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>9.86 ± 0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>5.62 ± 3.9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>0.00044 ± 0.00073</t>
         </is>
@@ -5601,40 +6111,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>0.0166 ± 0.016</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>0.412 ± 0.78</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>3.75 ± 2.1</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>0.00432 ± 0.014</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>0.0272 ± 0.03</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.00359 ± 0</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+          <t>0.00188 ± 0.0012</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>28.3 ± 8.5</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>0.000791 ± 0.0013</t>
         </is>
@@ -5649,40 +6164,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>0.219 ± 0.78</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>0.527 ± 1.1</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>0.0261 ± 0.05</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>0.000213 ± 0.00035</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>0.00158 ± 0.00071</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>10 ± 4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>0.0471 ± 0.18</t>
         </is>
@@ -5695,42 +6215,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>0.0122 ± 0.012</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>0.294 ± 0.54</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>0.000882 ± 0.0015</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>0.0204 ± 0.017</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>0.00182 ± 0.00068</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>4.93 ± 1.7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>0.000907 ± 0.0011</t>
         </is>
@@ -5749,40 +6274,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>0.024 ± 0.025</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>0.424 ± 0.88</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>0.307 ± 0.61</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>0.0127 ± 0.022</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>0.0148 ± 0.012</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.00428 ± 0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>0.00236 ± 0.0012</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>26.3 ± 5.6</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>0.000224 ± 0.00067</t>
         </is>
@@ -5797,40 +6327,45 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>0.027 ± 0.027</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>0.523 ± 1.1</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>0.0453 ± 0.063</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>0.000403 ± 0.0005</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>0.00244 ± 0.00092</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>11.2 ± 4.1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>0.0357 ± 0.13</t>
         </is>
@@ -5843,42 +6378,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>0.0191 ± 0.024</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>0.474 ± 1.1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>1.49 ± 3</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>0.025 ± 0.026</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>0.0147 ± 0.013</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>0.00284 ± 0.0018</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>7.34 ± 5.3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>0.00284 ± 0.0053</t>
         </is>
@@ -5895,42 +6435,47 @@
           <t>Heteroscedastic LVGP</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>0.0264 ± 0.024</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>0.00144 ± 0.0029</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>9.65 ± 6.6</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>0.00789 ± 0.019</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>6.33e-07 ± 4.8e-07</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>1.7e-06 ± 3e-06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>22.5 ± 8.3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>0.0178 ± 0.091</t>
         </is>
@@ -5945,40 +6490,45 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>0.73 ± 1.3</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>0.915 ± 2.1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>72.8 ± 60</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>0.102 ± 0.13</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>0.00188 ± 0.0038</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>0.00107 ± 0.00069</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>21.7 ± 12</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>0.195 ± 0.34</t>
         </is>
@@ -5993,40 +6543,45 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>0.111 ± 0.56</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>0.288 ± 1.1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>29 ± 47</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>0.00431 ± 0.014</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>1.23e-05 ± 2.5e-05</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>0.000688 ± 0.00052</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>8.77 ± 4.2</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>0.000752 ± 0.002</t>
         </is>
@@ -6051,19 +6606,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6079,40 +6635,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ackley_10d</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>ackley_2d</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>branin_hetero</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>golinski</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>otl_circuit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>piston</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>rastrigin_6d</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -6129,42 +6690,47 @@
           <t>Standard LVGP</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>0.00408 ± 0.0047</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>0.00407 ± 0.0032</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>3.48e-06 ± 1.1e-07</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>0.00381 ± 0.014</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>3.87e-06 ± 3.2e-06</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>2.16e-07 ± 1.5e-07</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>29.2 ± 7.3</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.0339 ± 0.13</t>
         </is>
@@ -6179,40 +6745,45 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>0.0188 ± 0.021</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1 ± 1.6</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1.72e-07 ± 1.8e-09</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.0097 ± 0.021</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>4.64e-07 ± 3.8e-07</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>4.6e-07 ± 5.1e-07</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>25.1 ± 5.7</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.034 ± 0.13</t>
         </is>
@@ -6227,40 +6798,45 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>1.38 ± 0.66</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>0.733 ± 1.3</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2.34 ± 3.4</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.0784 ± 0.1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.00188 ± 0.0038</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.00098 ± 0.00066</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>19.2 ± 11</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.207 ± 0.34</t>
         </is>
@@ -6273,42 +6849,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>1.25 ± 0.19</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.297 ± 0.88</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.77 ± 4.3</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.019 ± 0.064</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.00102 ± 0.00023</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>6.53 ± 4.3</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>0.0193 ± 0.1</t>
         </is>
@@ -6327,40 +6908,45 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>0.0131 ± 0.014</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>0.139 ± 0.74</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>72.5 ± 0</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>0.000902 ± 0.0012</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.056 ± 0.029</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>0.00122 ± 0.00051</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>20.7 ± 6.8</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>0.000115 ± 0.00017</t>
         </is>
@@ -6375,40 +6961,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>0.281 ± 1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2.41 ± 4.5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>1.37 ± 2.6</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>0.0436 ± 0.085</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.00586 ± 0.0099</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>2.93e-05 ± 3.7e-05</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>23.5 ± 3.1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.0513 ± 0.15</t>
         </is>
@@ -6423,40 +7014,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>1.74 ± 0.94</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>0.715 ± 1.3</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.72 ± 2.2</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>0.0343 ± 0.064</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>6.94e-05 ± 7e-05</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>0.000517 ± 0.00037</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>13.7 ± 3.8</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.0702 ± 0.2</t>
         </is>
@@ -6469,42 +7065,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>0.00491 ± 0.006</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>0.854 ± 3.3</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>0.00234 ± 0.01</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>0.0159 ± 0.011</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>0.00119 ± 0.0011</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>3.88 ± 2.8</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.000646 ± 0.0023</t>
         </is>
@@ -6523,40 +7124,45 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>0.0102 ± 0.0098</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>0.00449 ± 0.0035</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>62.9 ± 19</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>-6.55e-07 ± 4.2e-07</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>0.0666 ± 0.03</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>0.0024 ± 0.002</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>32.5 ± 11</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>1.67e-06 ± 5.6e-06</t>
         </is>
@@ -6571,40 +7177,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>0.022 ± 0.031</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>0.868 ± 1.7</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>6.77e-05 ± 8.2e-05</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>0.0218 ± 0.049</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>0.0124 ± 0.014</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>0.00106 ± 0.00057</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>31.4 ± 2.6</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0.0341 ± 0.13</t>
         </is>
@@ -6619,40 +7230,45 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>1.74 ± 0.92</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>0.426 ± 1.1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>1.81 ± 2</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>0.0278 ± 0.05</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>3.07e-05 ± 6.1e-05</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>0.00099 ± 0.00074</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>13.1 ± 9.6</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0.0467 ± 0.18</t>
         </is>
@@ -6665,42 +7281,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>0.01 ± 0.0092</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>0.765 ± 1.3</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>0.000174 ± 0.00025</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>0.0163 ± 0.014</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>0.002 ± 0.00056</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>3.91 ± 2.2</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0.000521 ± 0.00094</t>
         </is>
@@ -6719,40 +7340,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>0.0259 ± 0.023</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>0.17 ± 0.79</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>7.82 ± 4.1</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>0.00804 ± 0.019</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>0.0119 ± 0.013</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>0.00323 ± 0.0018</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>30.6 ± 5</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0.0171 ± 0.091</t>
         </is>
@@ -6767,40 +7393,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>2.39 ± 0.4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>0.429 ± 1.1</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>1.29 ± 1.8</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>0.0277 ± 0.05</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>3.07e-05 ± 6.1e-05</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>0.000791 ± 0.00055</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>9.43 ± 2.5</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0.0511 ± 0.15</t>
         </is>
@@ -6813,42 +7444,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>0.00801 ± 0.0085</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>0.0895 ± 0.19</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>0.00886 ± 0.02</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>0.0157 ± 0.013</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>0.00249 ± 0.00091</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>4.79 ± 1.6</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>0.000347 ± 0.00085</t>
         </is>
@@ -6867,40 +7503,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>0.0208 ± 0.019</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>0.00777 ± 0.022</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>0.965 ± 1.4</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>0.018 ± 0.026</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>0.00408 ± 0.0075</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>0.00165 ± 0.0013</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>24.3 ± 5.9</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>6.35e-05 ± 0.00015</t>
         </is>
@@ -6915,40 +7556,45 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>3.12 ± 1.3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>0.117 ± 0.56</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>1.42 ± 2.1</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>0.0392 ± 0.049</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>0.000202 ± 0.00037</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>0.00203 ± 0.00067</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>12.7 ± 3.5</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0.000237 ± 0.00042</t>
         </is>
@@ -6963,40 +7609,45 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>1.93 ± 0.24</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
           <t>0.00552 ± 0.0094</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>0.159 ± 0.47</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>0.0387 ± 0.05</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>0.0289 ± 0.017</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>0.00226 ± 0.00077</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>3.96 ± 2</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>0.000346 ± 0.00088</t>
         </is>
@@ -7013,42 +7664,47 @@
           <t>Heteroscedastic LVGP</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>0.0203 ± 0.025</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>0.00399 ± 0.012</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2.72 ± 2.4</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>0.00786 ± 0.019</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>2.74e-07 ± 1.7e-07</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>4.57e-07 ± 5.5e-07</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>20.7 ± 4.5</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>0.017 ± 0.091</t>
         </is>
@@ -7063,40 +7719,45 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>1.73 ± 1.1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>0.73 ± 1.3</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>0.581 ± 1.5</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>28.8 ± 51</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>0.0783 ± 0.1</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>0.00188 ± 0.0038</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>0.00115 ± 0.00057</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>21.2 ± 8.6</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>0.173 ± 0.3</t>
         </is>
@@ -7109,42 +7770,47 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>0.399 ± 0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>0.4 ± 1</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>0.717 ± 3.1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>10.6 ± 4</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>0.0403 ± 0.1</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>0.000695 ± 0.00033</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>5.2 ± 2.6</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>0.00022 ± 0.00055</t>
         </is>

--- a/benchmark/notebooks/acq_method_tables.xlsx
+++ b/benchmark/notebooks/acq_method_tables.xlsx
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.13 ± 0.23</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1827,9 +1827,9 @@
           <t>Heteroscedastic LVGP</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>0.655 ± 0.12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1933,9 +1933,9 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>1.25 ± 0.19</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.17 ± 0.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.477 ± 0.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.47 ± 0.73</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>1.93 ± 0.23</t>
+          <t>2.05 ± 0.32</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.28 ± 0</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>0.398 ± 0</t>
+          <t>0.579 ± 0.38</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0439 ± 0.0014</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.042 ± 0.00022</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0464 ± 0.002</t>
+          <t>0.0456 ± 0.0024</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0422 ± 0.0016</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0446 ± 0.0023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5096,7 +5096,7 @@
           <t>Separate GP</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>0.0321 ± 0.026</t>
         </is>
@@ -5149,9 +5149,9 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0.0459 ± 0.0012</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>0.032 ± 0.017</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0479 ± 0</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>0.0415 ± 0</t>
+          <t>0.0357 ± 0.013</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6611,7 +6611,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.14 ± 0.23</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -6743,9 +6743,9 @@
           <t>Heteroscedastic LVGP</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>0.657 ± 0.12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6849,9 +6849,9 @@
           <t>Categorical kernel</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>1.25 ± 0.19</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.18 ± 0.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.479 ± 0.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.48 ± 0.73</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>1.93 ± 0.24</t>
+          <t>2.04 ± 0.32</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.28 ± 0</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>0.399 ± 0</t>
+          <t>0.574 ± 0.37</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
